--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.84918076539315</v>
+        <v>9.725491874376388</v>
       </c>
       <c r="D2" t="n">
-        <v>58.34803021855569</v>
+        <v>9.4815549105153</v>
       </c>
       <c r="E2" t="n">
-        <v>9.29639673509705</v>
+        <v>1.510664469453271</v>
       </c>
       <c r="F2" t="n">
-        <v>8.90342536069749</v>
+        <v>1.446806621113342</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.5791121047832</v>
+        <v>6.106605717027271</v>
       </c>
       <c r="D3" t="n">
-        <v>37.28425368845933</v>
+        <v>6.058691224374641</v>
       </c>
       <c r="E3" t="n">
-        <v>9.29639673509705</v>
+        <v>1.510664469453271</v>
       </c>
       <c r="F3" t="n">
-        <v>8.90342536069749</v>
+        <v>1.446806621113342</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.82954393013561</v>
+        <v>8.584800888647038</v>
       </c>
       <c r="D4" t="n">
-        <v>52.71077298234122</v>
+        <v>8.565500609630448</v>
       </c>
       <c r="E4" t="n">
-        <v>9.29639673509705</v>
+        <v>1.510664469453271</v>
       </c>
       <c r="F4" t="n">
-        <v>8.90342536069749</v>
+        <v>1.446806621113342</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
